--- a/pepline/result/new_result.xlsx
+++ b/pepline/result/new_result.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACF92BC-B8FB-1644-8B07-00DA4B100BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8360" yWindow="29560" windowWidth="34560" windowHeight="20460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-29960" yWindow="0" windowWidth="29960" windowHeight="33840" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cecropin_A.z5_801-7_NCE28_dm1" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,20 @@
     <sheet name="LL37.Z7_642-79_NCE27_dm1_1000SC" sheetId="13" r:id="rId12"/>
     <sheet name="LL37.Z8_562.6_NCE26_dm1_1000SCA" sheetId="14" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
